--- a/update-ml-labreport-laboratoryobservation/ig/StructureDefinition-FRLMObservationAssessment.xlsx
+++ b/update-ml-labreport-laboratoryobservation/ig/StructureDefinition-FRLMObservationAssessment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T13:28:49+00:00</t>
+    <t>2026-09-16T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
